--- a/backtest_results.xlsx
+++ b/backtest_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kootony/Documents/GitHub/Trading-Algo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5112462B-DF30-D34F-B6C3-9AC6253B2D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142A454E-EA4F-014F-AD65-84CBAD13AF13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
